--- a/backtest_runs/20260410_193731/by_symbol/DAAG/DAAG.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/DAAG/DAAG.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>-9591.929999999995</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>94968.7</v>
@@ -955,7 +955,7 @@
         <v>-2077.440000000002</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>98880.12999999999</v>
@@ -1093,7 +1093,7 @@
         <v>-5161.139999999999</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>100925.11</v>
@@ -1231,7 +1231,7 @@
         <v>-7644.330000000002</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>99837.7</v>
@@ -1277,7 +1277,7 @@
         <v>-9364.710000000005</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>90472.98999999999</v>
@@ -1507,7 +1507,7 @@
         <v>-892.6499999999954</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>93800.14</v>
@@ -1645,7 +1645,7 @@
         <v>-7157.430000000006</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>102126.13</v>
